--- a/Current TAPPs/LA-Q-ICP-MS_TAPP_v29.xlsx
+++ b/Current TAPPs/LA-Q-ICP-MS_TAPP_v29.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description / Purpose</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Example/Allowed Content</t>
+          <t>Example / Allowed Content</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
